--- a/data/목차.xlsx
+++ b/data/목차.xlsx
@@ -603,13 +603,23 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>스토리보드</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+          <t>초고</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>19306</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -673,13 +683,23 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>설계</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+          <t>초고</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>16389</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>보류 — 장 1개 규격 밖</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
